--- a/jpcore-r4/main/CodeSystem-jp-dental-bodysite-cs.xlsx
+++ b/jpcore-r4/main/CodeSystem-jp-dental-bodysite-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/CodeSystem-jp-dental-bodysite-cs.xlsx
+++ b/jpcore-r4/main/CodeSystem-jp-dental-bodysite-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -144,625 +144,625 @@
     <t>1</t>
   </si>
   <si>
-    <t>TB-2-1011</t>
+    <t>1011</t>
   </si>
   <si>
     <t>右側上顎中切歯</t>
   </si>
   <si>
-    <t>TB-2-1012</t>
+    <t>1012</t>
   </si>
   <si>
     <t>右側上顎側切歯</t>
   </si>
   <si>
-    <t>TB-2-1013</t>
+    <t>1013</t>
   </si>
   <si>
     <t>右側上顎犬歯</t>
   </si>
   <si>
-    <t>TB-2-1014</t>
+    <t>1014</t>
   </si>
   <si>
     <t>右側上顎第１小臼歯</t>
   </si>
   <si>
-    <t>TB-2-1015</t>
+    <t>1015</t>
   </si>
   <si>
     <t>右側上顎第２小臼歯</t>
   </si>
   <si>
-    <t>TB-2-1016</t>
+    <t>1016</t>
   </si>
   <si>
     <t>右側上顎第１大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1017</t>
+    <t>1017</t>
   </si>
   <si>
     <t>右側上顎第２大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1018</t>
+    <t>1018</t>
   </si>
   <si>
     <t>右側上顎第３大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1021</t>
+    <t>1021</t>
   </si>
   <si>
     <t>左側上顎中切歯</t>
   </si>
   <si>
-    <t>TB-2-1022</t>
+    <t>1022</t>
   </si>
   <si>
     <t>左側上顎側切歯</t>
   </si>
   <si>
-    <t>TB-2-1023</t>
+    <t>1023</t>
   </si>
   <si>
     <t>左側上顎犬歯</t>
   </si>
   <si>
-    <t>TB-2-1024</t>
+    <t>1024</t>
   </si>
   <si>
     <t>左側上顎第１小臼歯</t>
   </si>
   <si>
-    <t>TB-2-1025</t>
+    <t>1025</t>
   </si>
   <si>
     <t>左側上顎第２小臼歯</t>
   </si>
   <si>
-    <t>TB-2-1026</t>
+    <t>1026</t>
   </si>
   <si>
     <t>左側上顎第１大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1027</t>
+    <t>1027</t>
   </si>
   <si>
     <t>左側上顎第２大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1028</t>
+    <t>1028</t>
   </si>
   <si>
     <t>左側上顎第３大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1031</t>
+    <t>1031</t>
   </si>
   <si>
     <t>左側下顎中切歯</t>
   </si>
   <si>
-    <t>TB-2-1032</t>
+    <t>1032</t>
   </si>
   <si>
     <t>左側下顎側切歯</t>
   </si>
   <si>
-    <t>TB-2-1033</t>
+    <t>1033</t>
   </si>
   <si>
     <t>左側下顎犬歯</t>
   </si>
   <si>
-    <t>TB-2-1034</t>
+    <t>1034</t>
   </si>
   <si>
     <t>左側下顎第１小臼歯</t>
   </si>
   <si>
-    <t>TB-2-1035</t>
+    <t>1035</t>
   </si>
   <si>
     <t>左側下顎第２小臼歯</t>
   </si>
   <si>
-    <t>TB-2-1036</t>
+    <t>1036</t>
   </si>
   <si>
     <t>左側下顎第１大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1037</t>
+    <t>1037</t>
   </si>
   <si>
     <t>左側下顎第２大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1038</t>
+    <t>1038</t>
   </si>
   <si>
     <t>左側下顎第３大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1041</t>
+    <t>1041</t>
   </si>
   <si>
     <t>右側下顎中切歯</t>
   </si>
   <si>
-    <t>TB-2-1042</t>
+    <t>1042</t>
   </si>
   <si>
     <t>右側下顎側切歯</t>
   </si>
   <si>
-    <t>TB-2-1043</t>
+    <t>1043</t>
   </si>
   <si>
     <t>右側下顎犬歯</t>
   </si>
   <si>
-    <t>TB-2-1044</t>
+    <t>1044</t>
   </si>
   <si>
     <t>右側下顎第１小臼歯</t>
   </si>
   <si>
-    <t>TB-2-1045</t>
+    <t>1045</t>
   </si>
   <si>
     <t>右側下顎第２小臼歯</t>
   </si>
   <si>
-    <t>TB-2-1046</t>
+    <t>1046</t>
   </si>
   <si>
     <t>右側下顎第１大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1047</t>
+    <t>1047</t>
   </si>
   <si>
     <t>右側下顎第２大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1048</t>
+    <t>1048</t>
   </si>
   <si>
     <t>右側下顎第３大臼歯</t>
   </si>
   <si>
-    <t>TB-2-1051</t>
+    <t>1051</t>
   </si>
   <si>
     <t>右側上顎乳中切歯</t>
   </si>
   <si>
-    <t>TB-2-1052</t>
+    <t>1052</t>
   </si>
   <si>
     <t>右側上顎乳側切歯</t>
   </si>
   <si>
-    <t>TB-2-1053</t>
+    <t>1053</t>
   </si>
   <si>
     <t>右側上顎乳犬歯</t>
   </si>
   <si>
-    <t>TB-2-1054</t>
+    <t>1054</t>
   </si>
   <si>
     <t>右側上顎第１乳臼歯</t>
   </si>
   <si>
-    <t>TB-2-1055</t>
+    <t>1055</t>
   </si>
   <si>
     <t>右側上顎第２乳臼歯</t>
   </si>
   <si>
-    <t>TB-2-1061</t>
+    <t>1061</t>
   </si>
   <si>
     <t>左側上顎乳中切歯</t>
   </si>
   <si>
-    <t>TB-2-1062</t>
+    <t>1062</t>
   </si>
   <si>
     <t>左側上顎乳側切歯</t>
   </si>
   <si>
-    <t>TB-2-1063</t>
+    <t>1063</t>
   </si>
   <si>
     <t>左側上顎乳犬歯</t>
   </si>
   <si>
-    <t>TB-2-1064</t>
+    <t>1064</t>
   </si>
   <si>
     <t>左側上顎第１乳臼歯</t>
   </si>
   <si>
-    <t>TB-2-1065</t>
+    <t>1065</t>
   </si>
   <si>
     <t>左側上顎第２乳臼歯</t>
   </si>
   <si>
-    <t>TB-2-1071</t>
+    <t>1071</t>
   </si>
   <si>
     <t>左側下顎乳中切歯</t>
   </si>
   <si>
-    <t>TB-2-1072</t>
+    <t>1072</t>
   </si>
   <si>
     <t>左側下顎乳側切歯</t>
   </si>
   <si>
-    <t>TB-2-1073</t>
+    <t>1073</t>
   </si>
   <si>
     <t>左側下顎乳犬歯</t>
   </si>
   <si>
-    <t>TB-2-1074</t>
+    <t>1074</t>
   </si>
   <si>
     <t>左側下顎第１乳臼歯</t>
   </si>
   <si>
-    <t>TB-2-1075</t>
+    <t>1075</t>
   </si>
   <si>
     <t>左側下顎第２乳臼歯</t>
   </si>
   <si>
-    <t>TB-2-1081</t>
+    <t>1081</t>
   </si>
   <si>
     <t>右側下顎乳中切歯</t>
   </si>
   <si>
-    <t>TB-2-1082</t>
+    <t>1082</t>
   </si>
   <si>
     <t>右側下顎乳側切歯</t>
   </si>
   <si>
-    <t>TB-2-1083</t>
+    <t>1083</t>
   </si>
   <si>
     <t>右側下顎乳犬歯</t>
   </si>
   <si>
-    <t>TB-2-1084</t>
+    <t>1084</t>
   </si>
   <si>
     <t>右側下顎第１乳臼歯</t>
   </si>
   <si>
-    <t>TB-2-1085</t>
+    <t>1085</t>
   </si>
   <si>
     <t>右側下顎第２乳臼歯</t>
   </si>
   <si>
-    <t>TB-2-101A</t>
+    <t>101A</t>
   </si>
   <si>
     <t>右側上顎中切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-101B</t>
+    <t>101B</t>
   </si>
   <si>
     <t>右側上顎側切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-101C</t>
+    <t>101C</t>
   </si>
   <si>
     <t>右側上顎犬歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-101D</t>
+    <t>101D</t>
   </si>
   <si>
     <t>右側上顎第１小臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-101E</t>
+    <t>101E</t>
   </si>
   <si>
     <t>右側上顎第２小臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-101F</t>
+    <t>101F</t>
   </si>
   <si>
     <t>右側上顎第１大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-101G</t>
+    <t>101G</t>
   </si>
   <si>
     <t>右側上顎第２大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-101H</t>
+    <t>101H</t>
   </si>
   <si>
     <t>右側上顎第３大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-102A</t>
+    <t>102A</t>
   </si>
   <si>
     <t>左側上顎中切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-102B</t>
+    <t>102B</t>
   </si>
   <si>
     <t>左側上顎側切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-102C</t>
+    <t>102C</t>
   </si>
   <si>
     <t>左側上顎犬歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-102D</t>
+    <t>102D</t>
   </si>
   <si>
     <t>左側上顎第１小臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-102E</t>
+    <t>102E</t>
   </si>
   <si>
     <t>左側上顎第２小臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-102F</t>
+    <t>102F</t>
   </si>
   <si>
     <t>左側上顎第１大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-102G</t>
+    <t>102G</t>
   </si>
   <si>
     <t>左側上顎第２大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-102H</t>
+    <t>102H</t>
   </si>
   <si>
     <t>左側上顎第３大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-103A</t>
+    <t>103A</t>
   </si>
   <si>
     <t>左側下顎中切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-103B</t>
+    <t>103B</t>
   </si>
   <si>
     <t>左側下顎側切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-103C</t>
+    <t>103C</t>
   </si>
   <si>
     <t>左側下顎犬歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-103D</t>
+    <t>103D</t>
   </si>
   <si>
     <t>左側下顎第１小臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-103E</t>
+    <t>103E</t>
   </si>
   <si>
     <t>左側下顎第２小臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-103F</t>
+    <t>103F</t>
   </si>
   <si>
     <t>左側下顎第１大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-103G</t>
+    <t>103G</t>
   </si>
   <si>
     <t>左側下顎第２大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-103H</t>
+    <t>103H</t>
   </si>
   <si>
     <t>左側下顎第３大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-104A</t>
+    <t>104A</t>
   </si>
   <si>
     <t>右側下顎中切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-104B</t>
+    <t>104B</t>
   </si>
   <si>
     <t>右側下顎側切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-104C</t>
+    <t>104C</t>
   </si>
   <si>
     <t>右側下顎犬歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-104D</t>
+    <t>104D</t>
   </si>
   <si>
     <t>右側下顎第１小臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-104E</t>
+    <t>104E</t>
   </si>
   <si>
     <t>右側下顎第２小臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-104F</t>
+    <t>104F</t>
   </si>
   <si>
     <t>右側下顎第１大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-104G</t>
+    <t>104G</t>
   </si>
   <si>
     <t>右側下顎第２大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-104H</t>
+    <t>104H</t>
   </si>
   <si>
     <t>右側下顎第３大臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-105A</t>
+    <t>105A</t>
   </si>
   <si>
     <t>右側上顎乳中切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-105B</t>
+    <t>105B</t>
   </si>
   <si>
     <t>右側上顎乳側切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-105C</t>
+    <t>105C</t>
   </si>
   <si>
     <t>右側上顎乳犬歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-105D</t>
+    <t>105D</t>
   </si>
   <si>
     <t>右側上顎第１乳臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-105E</t>
+    <t>105E</t>
   </si>
   <si>
     <t>右側上顎第２乳臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-106A</t>
+    <t>106A</t>
   </si>
   <si>
     <t>左側上顎乳中切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-106B</t>
+    <t>106B</t>
   </si>
   <si>
     <t>左側上顎乳側切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-106C</t>
+    <t>106C</t>
   </si>
   <si>
     <t>左側上顎乳犬歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-106D</t>
+    <t>106D</t>
   </si>
   <si>
     <t>左側上顎第１乳臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-106E</t>
+    <t>106E</t>
   </si>
   <si>
     <t>左側上顎第２乳臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-107A</t>
+    <t>107A</t>
   </si>
   <si>
     <t>左側下顎乳中切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-107B</t>
+    <t>107B</t>
   </si>
   <si>
     <t>左側下顎乳側切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-107C</t>
+    <t>107C</t>
   </si>
   <si>
     <t>左側下顎乳犬歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-107D</t>
+    <t>107D</t>
   </si>
   <si>
     <t>左側下顎第１乳臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-107E</t>
+    <t>107E</t>
   </si>
   <si>
     <t>左側下顎第２乳臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-108A</t>
+    <t>108A</t>
   </si>
   <si>
     <t>右側下顎乳中切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-108B</t>
+    <t>108B</t>
   </si>
   <si>
     <t>右側下顎乳側切歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-108C</t>
+    <t>108C</t>
   </si>
   <si>
     <t>右側下顎乳犬歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-108D</t>
+    <t>108D</t>
   </si>
   <si>
     <t>右側下顎第１乳臼歯近傍過剰歯</t>
   </si>
   <si>
-    <t>TB-2-108E</t>
+    <t>108E</t>
   </si>
   <si>
     <t>右側下顎第２乳臼歯近傍過剰歯</t>

--- a/jpcore-r4/main/CodeSystem-jp-dental-bodysite-cs.xlsx
+++ b/jpcore-r4/main/CodeSystem-jp-dental-bodysite-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/CodeSystem-jp-dental-bodysite-cs.xlsx
+++ b/jpcore-r4/main/CodeSystem-jp-dental-bodysite-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/CodeSystem-jp-dental-bodysite-cs.xlsx
+++ b/jpcore-r4/main/CodeSystem-jp-dental-bodysite-cs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright Japan Dental Association 日本歯科医師会 &amp; FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan Dental Association 日本歯科医師会 &amp; FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>Case Sensitive</t>
